--- a/docs/all/idx13_saludmental_loadings_y_tops.xlsx
+++ b/docs/all/idx13_saludmental_loadings_y_tops.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.4006678923088532</v>
+        <v>-0.400667892308853</v>
       </c>
       <c r="D6">
         <v>0.1359694080673226</v>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.4232308246826642</v>
+        <v>-0.4232308246826641</v>
       </c>
       <c r="D7">
         <v>0.1436262945262088</v>
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="C8">
-        <v>-0.05525082846893625</v>
+        <v>-0.05525082846893629</v>
       </c>
       <c r="D8">
-        <v>0.01874974907238017</v>
+        <v>0.01874974907238019</v>
       </c>
       <c r="E8">
         <v>1.9</v>
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="C9">
-        <v>-0.1119877018990237</v>
+        <v>-0.1119877018990239</v>
       </c>
       <c r="D9">
-        <v>0.0380037977345398</v>
+        <v>0.03800379773453986</v>
       </c>
       <c r="E9">
         <v>3.8</v>
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.1061030748001057</v>
+        <v>-0.1061030748001056</v>
       </c>
       <c r="D10">
-        <v>0.03600680900972322</v>
+        <v>0.0360068090097232</v>
       </c>
       <c r="E10">
         <v>3.6</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>-0.1289025074023538</v>
+        <v>-0.1289025074023539</v>
       </c>
       <c r="D11">
         <v>0.04374395344955984</v>
@@ -606,10 +606,10 @@
         </is>
       </c>
       <c r="C12">
-        <v>-0.04559303836835236</v>
+        <v>-0.04559303836835241</v>
       </c>
       <c r="D12">
-        <v>0.0154723115027069</v>
+        <v>0.01547231150270692</v>
       </c>
       <c r="E12">
         <v>1.5</v>
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.1401184370006759</v>
+        <v>-0.140118437000676</v>
       </c>
       <c r="D13">
-        <v>0.04755015638641271</v>
+        <v>0.04755015638641277</v>
       </c>
       <c r="E13">
         <v>4.8</v>
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="C14">
-        <v>-0.1422905354698256</v>
+        <v>-0.1422905354698257</v>
       </c>
       <c r="D14">
-        <v>0.04896798282770726</v>
+        <v>0.04896798282770724</v>
       </c>
       <c r="E14">
         <v>4.9</v>
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="C15">
-        <v>-0.1233776143736372</v>
+        <v>-0.1233776143736376</v>
       </c>
       <c r="D15">
-        <v>0.04245927448388115</v>
+        <v>0.04245927448388125</v>
       </c>
       <c r="E15">
         <v>4.2</v>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="C16">
-        <v>0.06252568610109425</v>
+        <v>0.06252568610109509</v>
       </c>
       <c r="D16">
-        <v>0.02151764144522654</v>
+        <v>0.02151764144522682</v>
       </c>
       <c r="E16">
         <v>2.2</v>
@@ -714,7 +714,7 @@
         <v>-0.1309893165558222</v>
       </c>
       <c r="D17">
-        <v>0.04507877198254578</v>
+        <v>0.04507877198254574</v>
       </c>
       <c r="E17">
         <v>4.5</v>
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="C18">
-        <v>-0.09725872052002722</v>
+        <v>-0.0972587205200274</v>
       </c>
       <c r="D18">
-        <v>0.03347069670195618</v>
+        <v>0.03347069670195622</v>
       </c>
       <c r="E18">
         <v>3.3</v>
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="C19">
-        <v>-0.1464609058589733</v>
+        <v>-0.1464609058589735</v>
       </c>
       <c r="D19">
-        <v>0.05040317755043897</v>
+        <v>0.05040317755043899</v>
       </c>
       <c r="E19">
         <v>5</v>
@@ -777,7 +777,7 @@
         <v>0.3294957945370715</v>
       </c>
       <c r="D20">
-        <v>0.1133929558660958</v>
+        <v>0.1133929558660957</v>
       </c>
       <c r="E20">
         <v>11.3</v>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.4957886174245391</v>
+        <v>0.4957886174245394</v>
       </c>
       <c r="D21">
         <v>0.1706211057823023</v>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.3489079910685441</v>
+        <v>0.3489079910685439</v>
       </c>
       <c r="D22">
-        <v>0.1200734852720928</v>
+        <v>0.1200734852720926</v>
       </c>
       <c r="E22">
         <v>12</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.4511848358771115</v>
+        <v>0.4511848358771114</v>
       </c>
       <c r="D23">
-        <v>0.1552711234264595</v>
+        <v>0.1552711234264594</v>
       </c>
       <c r="E23">
         <v>15.5</v>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="C24">
-        <v>0.1069321872223359</v>
+        <v>0.1069321872223361</v>
       </c>
       <c r="D24">
-        <v>0.03679973155166691</v>
+        <v>0.03679973155166694</v>
       </c>
       <c r="E24">
         <v>3.7</v>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="C25">
-        <v>0.4705749492316099</v>
+        <v>0.4705749492316103</v>
       </c>
       <c r="D25">
         <v>0.1619440531096269</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="C26">
-        <v>0.008540230220584189</v>
+        <v>0.008540230220584533</v>
       </c>
       <c r="D26">
-        <v>0.003855839871472304</v>
+        <v>0.003855839871472459</v>
       </c>
       <c r="E26">
         <v>0.4</v>
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="C27">
-        <v>0.02382846607256266</v>
+        <v>0.02382846607256268</v>
       </c>
       <c r="D27">
-        <v>0.010758345757139</v>
+        <v>0.01075834575713901</v>
       </c>
       <c r="E27">
         <v>1.1</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="C28">
-        <v>-0.03974948355946038</v>
+        <v>-0.03974948355946101</v>
       </c>
       <c r="D28">
-        <v>0.01794654706258211</v>
+        <v>0.0179465470625824</v>
       </c>
       <c r="E28">
         <v>1.8</v>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="C29">
-        <v>0.02921420817894116</v>
+        <v>0.02921420817894115</v>
       </c>
       <c r="D29">
-        <v>0.01318996160529127</v>
+        <v>0.01318996160529126</v>
       </c>
       <c r="E29">
         <v>1.3</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="C30">
-        <v>-0.0364923206795111</v>
+        <v>-0.03649232067951099</v>
       </c>
       <c r="D30">
-        <v>0.01647596627307163</v>
+        <v>0.01647596627307158</v>
       </c>
       <c r="E30">
         <v>1.6</v>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="C31">
-        <v>0.0158195326690369</v>
+        <v>0.01581953266903686</v>
       </c>
       <c r="D31">
-        <v>0.007142381790400802</v>
+        <v>0.007142381790400786</v>
       </c>
       <c r="E31">
         <v>0.7</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="C32">
-        <v>0.4162015856096426</v>
+        <v>0.4162015856096414</v>
       </c>
       <c r="D32">
-        <v>0.1879114060058533</v>
+        <v>0.1879114060058527</v>
       </c>
       <c r="E32">
         <v>18.8</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C33">
-        <v>-0.03180828949712979</v>
+        <v>-0.0318082894971303</v>
       </c>
       <c r="D33">
-        <v>0.01436116682086085</v>
+        <v>0.01436116682086108</v>
       </c>
       <c r="E33">
         <v>1.4</v>
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="C34">
-        <v>-0.4353114575741731</v>
+        <v>-0.4353114575741723</v>
       </c>
       <c r="D34">
-        <v>0.1965393474496293</v>
+        <v>0.196539347449629</v>
       </c>
       <c r="E34">
         <v>19.7</v>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="C35">
-        <v>-0.2724990014749152</v>
+        <v>-0.2724990014749154</v>
       </c>
       <c r="D35">
-        <v>0.1230309356638743</v>
+        <v>0.1230309356638744</v>
       </c>
       <c r="E35">
         <v>12.3</v>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="C36">
-        <v>0.7242470942393084</v>
+        <v>0.7242470942393091</v>
       </c>
       <c r="D36">
-        <v>0.3269912813398208</v>
+        <v>0.3269912813398211</v>
       </c>
       <c r="E36">
         <v>32.7</v>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="C37">
-        <v>0.1811703028319655</v>
+        <v>0.1811703028319657</v>
       </c>
       <c r="D37">
-        <v>0.08179682036000421</v>
+        <v>0.0817968203600043</v>
       </c>
       <c r="E37">
         <v>8.199999999999999</v>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="C38">
-        <v>0.08916924798021737</v>
+        <v>0.08916924798021748</v>
       </c>
       <c r="D38">
-        <v>0.03404798452791329</v>
+        <v>0.03404798452791335</v>
       </c>
       <c r="E38">
         <v>3.4</v>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="C39">
-        <v>0.009679236960842936</v>
+        <v>0.009679236960842556</v>
       </c>
       <c r="D39">
-        <v>0.003695876299841632</v>
+        <v>0.003695876299841489</v>
       </c>
       <c r="E39">
         <v>0.4</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="C40">
-        <v>-0.1877749985934389</v>
+        <v>-0.1877749985934384</v>
       </c>
       <c r="D40">
-        <v>0.07169916077184751</v>
+        <v>0.07169916077184739</v>
       </c>
       <c r="E40">
         <v>7.2</v>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="C41">
-        <v>-0.2319815181235838</v>
+        <v>-0.2319815181235837</v>
       </c>
       <c r="D41">
-        <v>0.08857877932968478</v>
+        <v>0.0885787793296848</v>
       </c>
       <c r="E41">
         <v>8.9</v>
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.1594931596869123</v>
+        <v>0.1594931596869124</v>
       </c>
       <c r="D42">
-        <v>0.06090015062740865</v>
+        <v>0.06090015062740871</v>
       </c>
       <c r="E42">
         <v>6.1</v>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="C43">
-        <v>0.008253451970829615</v>
+        <v>0.008253451970829547</v>
       </c>
       <c r="D43">
-        <v>0.00315146097303665</v>
+        <v>0.003151460973036625</v>
       </c>
       <c r="E43">
         <v>0.3</v>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="C44">
-        <v>-0.5769074247658514</v>
+        <v>-0.5769074247658522</v>
       </c>
       <c r="D44">
-        <v>0.2202837358998901</v>
+        <v>0.2202837358998904</v>
       </c>
       <c r="E44">
         <v>22</v>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="C45">
-        <v>-0.04011797397546521</v>
+        <v>-0.04011797397546518</v>
       </c>
       <c r="D45">
         <v>0.01531846671523917</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="C46">
-        <v>0.4719927763927749</v>
+        <v>0.4719927763927753</v>
       </c>
       <c r="D46">
-        <v>0.1802235985154134</v>
+        <v>0.1802235985154136</v>
       </c>
       <c r="E46">
         <v>18</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="C47">
-        <v>-0.1648274683426583</v>
+        <v>-0.1648274683426579</v>
       </c>
       <c r="D47">
-        <v>0.06293697904855051</v>
+        <v>0.06293697904855038</v>
       </c>
       <c r="E47">
         <v>6.3</v>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="C48">
-        <v>0.5163670861300702</v>
+        <v>0.5163670861300691</v>
       </c>
       <c r="D48">
-        <v>0.1971672853311579</v>
+        <v>0.1971672853311576</v>
       </c>
       <c r="E48">
         <v>19.7</v>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="C49">
-        <v>0.162364478168497</v>
+        <v>0.1623644781684966</v>
       </c>
       <c r="D49">
-        <v>0.06199652196001645</v>
+        <v>0.06199652196001636</v>
       </c>
       <c r="E49">
         <v>6.2</v>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="C50">
-        <v>-0.2946096151076015</v>
+        <v>-0.2946096151076016</v>
       </c>
       <c r="D50">
-        <v>0.1391784208634372</v>
+        <v>0.1391784208634373</v>
       </c>
       <c r="E50">
         <v>13.9</v>
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="C51">
-        <v>-0.08478951771565434</v>
+        <v>-0.08478951771565409</v>
       </c>
       <c r="D51">
-        <v>0.04005596075717732</v>
+        <v>0.04005596075717721</v>
       </c>
       <c r="E51">
         <v>4</v>
@@ -1446,10 +1446,10 @@
         </is>
       </c>
       <c r="C52">
-        <v>0.8984701804440338</v>
+        <v>0.898470180444034</v>
       </c>
       <c r="D52">
-        <v>0.4244520697717771</v>
+        <v>0.4244520697717773</v>
       </c>
       <c r="E52">
         <v>42.4</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="C53">
-        <v>-0.04665126910900332</v>
+        <v>-0.04665126910900372</v>
       </c>
       <c r="D53">
-        <v>0.02203882573043286</v>
+        <v>0.02203882573043305</v>
       </c>
       <c r="E53">
         <v>2.2</v>
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="C54">
-        <v>-0.09190398892655</v>
+        <v>-0.09190398892654955</v>
       </c>
       <c r="D54">
-        <v>0.04341695380572123</v>
+        <v>0.04341695380572103</v>
       </c>
       <c r="E54">
         <v>4.3</v>
@@ -1512,7 +1512,7 @@
         <v>-0.1287201333196082</v>
       </c>
       <c r="D55">
-        <v>0.06080950508764276</v>
+        <v>0.06080950508764279</v>
       </c>
       <c r="E55">
         <v>6.1</v>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="C56">
-        <v>-0.1713256115898944</v>
+        <v>-0.1713256115898941</v>
       </c>
       <c r="D56">
-        <v>0.0809370327775458</v>
+        <v>0.08093703277754564</v>
       </c>
       <c r="E56">
         <v>8.1</v>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="C57">
-        <v>-0.06643160980270581</v>
+        <v>-0.06643160980270582</v>
       </c>
       <c r="D57">
-        <v>0.03138338354768132</v>
+        <v>0.03138338354768133</v>
       </c>
       <c r="E57">
         <v>3.1</v>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="C58">
-        <v>0.03366796952180263</v>
+        <v>0.0336679695218026</v>
       </c>
       <c r="D58">
-        <v>0.01590530176692091</v>
+        <v>0.0159053017669209</v>
       </c>
       <c r="E58">
         <v>1.6</v>
@@ -1596,7 +1596,7 @@
         <v>-0.1386247078056078</v>
       </c>
       <c r="D59">
-        <v>0.06548858874817515</v>
+        <v>0.06548858874817517</v>
       </c>
       <c r="E59">
         <v>6.5</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="C60">
-        <v>0.1277237076647742</v>
+        <v>0.127723707664774</v>
       </c>
       <c r="D60">
-        <v>0.06033877724294238</v>
+        <v>0.06033877724294229</v>
       </c>
       <c r="E60">
         <v>6</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="C61">
-        <v>-0.03385822144584069</v>
+        <v>-0.03385822144584078</v>
       </c>
       <c r="D61">
-        <v>0.0159951799005459</v>
+        <v>0.01599517990054594</v>
       </c>
       <c r="E61">
         <v>1.6</v>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="C62">
-        <v>-0.04380535808092624</v>
+        <v>-0.04380535808092627</v>
       </c>
       <c r="D62">
-        <v>0.02044053667597668</v>
+        <v>0.02044053667597669</v>
       </c>
       <c r="E62">
         <v>2</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="C63">
-        <v>-0.01694235873901458</v>
+        <v>-0.01694235873901441</v>
       </c>
       <c r="D63">
-        <v>0.00790567456480107</v>
+        <v>0.007905674564800989</v>
       </c>
       <c r="E63">
         <v>0.8</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="C64">
-        <v>-0.09791678750958588</v>
+        <v>-0.09791678750958549</v>
       </c>
       <c r="D64">
-        <v>0.04569011130067643</v>
+        <v>0.04569011130067624</v>
       </c>
       <c r="E64">
         <v>4.6</v>
@@ -1719,7 +1719,7 @@
         </is>
       </c>
       <c r="C65">
-        <v>0.7668100639004388</v>
+        <v>0.7668100639004392</v>
       </c>
       <c r="D65">
         <v>0.3578103209591096</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="C66">
-        <v>-0.5559430186374205</v>
+        <v>-0.555943018637421</v>
       </c>
       <c r="D66">
-        <v>0.2594151528499754</v>
+        <v>0.2594151528499755</v>
       </c>
       <c r="E66">
         <v>25.9</v>
@@ -1761,10 +1761,10 @@
         </is>
       </c>
       <c r="C67">
-        <v>-0.04331467690121155</v>
+        <v>-0.04331467690121185</v>
       </c>
       <c r="D67">
-        <v>0.02021157412231737</v>
+        <v>0.0202115741223175</v>
       </c>
       <c r="E67">
         <v>2</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C68">
-        <v>-0.1397584573431823</v>
+        <v>-0.1397584573431827</v>
       </c>
       <c r="D68">
-        <v>0.06521434815859031</v>
+        <v>0.06521434815859045</v>
       </c>
       <c r="E68">
         <v>6.5</v>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="C69">
-        <v>0.06533037581885423</v>
+        <v>0.06533037581885416</v>
       </c>
       <c r="D69">
-        <v>0.03048458000305871</v>
+        <v>0.03048458000305866</v>
       </c>
       <c r="E69">
         <v>3</v>
@@ -1827,7 +1827,7 @@
         <v>0.2123643184057799</v>
       </c>
       <c r="D70">
-        <v>0.09909382845410927</v>
+        <v>0.09909382845410926</v>
       </c>
       <c r="E70">
         <v>9.9</v>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="C71">
-        <v>-0.0737292479168648</v>
+        <v>-0.07372924791686462</v>
       </c>
       <c r="D71">
-        <v>0.03440367713357559</v>
+        <v>0.03440367713357548</v>
       </c>
       <c r="E71">
         <v>3.4</v>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="C72">
-        <v>0.1220610664123432</v>
+        <v>0.1220610664123431</v>
       </c>
       <c r="D72">
-        <v>0.05695635908513894</v>
+        <v>0.05695635908513887</v>
       </c>
       <c r="E72">
         <v>5.7</v>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="C73">
-        <v>-0.005087281610873219</v>
+        <v>-0.005087281610873412</v>
       </c>
       <c r="D73">
-        <v>0.002373836692670566</v>
+        <v>0.002373836692670655</v>
       </c>
       <c r="E73">
         <v>0.2</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="C74">
-        <v>0.07911455759958322</v>
+        <v>0.07911455759958351</v>
       </c>
       <c r="D74">
-        <v>0.03121602700733839</v>
+        <v>0.03121602700733852</v>
       </c>
       <c r="E74">
         <v>3.1</v>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="C75">
-        <v>0.04369833411198309</v>
+        <v>0.04369833411198286</v>
       </c>
       <c r="D75">
-        <v>0.01724193902112583</v>
+        <v>0.01724193902112574</v>
       </c>
       <c r="E75">
         <v>1.7</v>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="C76">
-        <v>0.01061065817954676</v>
+        <v>0.01061065817954654</v>
       </c>
       <c r="D76">
-        <v>0.004186620039952201</v>
+        <v>0.004186620039952117</v>
       </c>
       <c r="E76">
         <v>0.4</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="C77">
-        <v>-0.08460795448448524</v>
+        <v>-0.08460795448448497</v>
       </c>
       <c r="D77">
-        <v>0.0333835424523345</v>
+        <v>0.0333835424523344</v>
       </c>
       <c r="E77">
         <v>3.3</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="C78">
-        <v>0.06187885462648504</v>
+        <v>0.06187885462648512</v>
       </c>
       <c r="D78">
-        <v>0.02441538012485454</v>
+        <v>0.02441538012485458</v>
       </c>
       <c r="E78">
         <v>2.4</v>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="C79">
-        <v>-0.05177099791892291</v>
+        <v>-0.05177099791892312</v>
       </c>
       <c r="D79">
-        <v>0.02042714916530698</v>
+        <v>0.02042714916530707</v>
       </c>
       <c r="E79">
         <v>2</v>
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="C80">
-        <v>0.323851856875646</v>
+        <v>0.3238518568756458</v>
       </c>
       <c r="D80">
-        <v>0.1277813921651774</v>
+        <v>0.1277813921651773</v>
       </c>
       <c r="E80">
         <v>12.8</v>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="C81">
-        <v>0.4772517389823757</v>
+        <v>0.4772517389823762</v>
       </c>
       <c r="D81">
-        <v>0.1883079881300068</v>
+        <v>0.188307988130007</v>
       </c>
       <c r="E81">
         <v>18.8</v>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="C82">
-        <v>0.3644315338288301</v>
+        <v>0.3644315338288298</v>
       </c>
       <c r="D82">
-        <v>0.1437928106721341</v>
+        <v>0.143792810672134</v>
       </c>
       <c r="E82">
         <v>14.4</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="C83">
-        <v>-0.5438502306704468</v>
+        <v>-0.543850230670447</v>
       </c>
       <c r="D83">
-        <v>0.2145855832813924</v>
+        <v>0.2145855832813926</v>
       </c>
       <c r="E83">
         <v>21.5</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="C84">
-        <v>-0.02859569125167374</v>
+        <v>-0.02859569125167335</v>
       </c>
       <c r="D84">
-        <v>0.01128292816757735</v>
+        <v>0.01128292816757719</v>
       </c>
       <c r="E84">
         <v>1.1</v>
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="C85">
-        <v>-0.4647586944817732</v>
+        <v>-0.464758694481773</v>
       </c>
       <c r="D85">
-        <v>0.1833786397727995</v>
+        <v>0.1833786397727994</v>
       </c>
       <c r="E85">
         <v>18.3</v>
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="C86">
-        <v>0.7122871693927643</v>
+        <v>0.7122871693927653</v>
       </c>
       <c r="D86">
-        <v>0.3111416877537692</v>
+        <v>0.3111416877537696</v>
       </c>
       <c r="E86">
         <v>31.1</v>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="C87">
-        <v>0.1687527069057849</v>
+        <v>0.1687527069057836</v>
       </c>
       <c r="D87">
-        <v>0.07371465371816993</v>
+        <v>0.07371465371816936</v>
       </c>
       <c r="E87">
         <v>7.4</v>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="C88">
-        <v>0.157204381356628</v>
+        <v>0.1572043813566282</v>
       </c>
       <c r="D88">
-        <v>0.06867010756249804</v>
+        <v>0.06867010756249814</v>
       </c>
       <c r="E88">
         <v>6.9</v>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="C89">
-        <v>-0.3183761606795967</v>
+        <v>-0.3183761606795962</v>
       </c>
       <c r="D89">
-        <v>0.1390732561683866</v>
+        <v>0.1390732561683864</v>
       </c>
       <c r="E89">
         <v>13.9</v>
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="C90">
-        <v>-0.5395109304965499</v>
+        <v>-0.5395109304965491</v>
       </c>
       <c r="D90">
-        <v>0.2356694724957771</v>
+        <v>0.2356694724957767</v>
       </c>
       <c r="E90">
         <v>23.6</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="C91">
-        <v>-0.1919588054942327</v>
+        <v>-0.1919588054942334</v>
       </c>
       <c r="D91">
-        <v>0.0838515549446029</v>
+        <v>0.08385155494460322</v>
       </c>
       <c r="E91">
         <v>8.4</v>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="C92">
-        <v>0.01323967611626682</v>
+        <v>0.0132396761162668</v>
       </c>
       <c r="D92">
-        <v>0.005783362875454278</v>
+        <v>0.005783362875454272</v>
       </c>
       <c r="E92">
         <v>0.6</v>
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="C93">
-        <v>-0.07975901048279369</v>
+        <v>-0.0797590104827941</v>
       </c>
       <c r="D93">
-        <v>0.03484037646830465</v>
+        <v>0.03484037646830483</v>
       </c>
       <c r="E93">
         <v>3.5</v>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="C94">
-        <v>-0.00747069796087116</v>
+        <v>-0.007470697960871163</v>
       </c>
       <c r="D94">
-        <v>0.003263354545928041</v>
+        <v>0.003263354545928043</v>
       </c>
       <c r="E94">
         <v>0.3</v>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="C95">
-        <v>0.02385651364713223</v>
+        <v>0.02385651364713261</v>
       </c>
       <c r="D95">
-        <v>0.01042101590348393</v>
+        <v>0.0104210159034841</v>
       </c>
       <c r="E95">
         <v>1</v>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="C96">
-        <v>-0.0330540988384467</v>
+        <v>-0.03305409883844688</v>
       </c>
       <c r="D96">
-        <v>0.01443871031474834</v>
+        <v>0.01443871031474842</v>
       </c>
       <c r="E96">
         <v>1.4</v>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="C97">
-        <v>0.04379932754380256</v>
+        <v>0.04379932754380253</v>
       </c>
       <c r="D97">
-        <v>0.01913244724887686</v>
+        <v>0.01913244724887684</v>
       </c>
       <c r="E97">
         <v>1.9</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="C98">
-        <v>-0.3831458346142005</v>
+        <v>-0.3831458346141994</v>
       </c>
       <c r="D98">
-        <v>0.1621539504416636</v>
+        <v>0.1621539504416631</v>
       </c>
       <c r="E98">
         <v>16.2</v>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="C99">
-        <v>0.4598126710276688</v>
+        <v>0.45981267102767</v>
       </c>
       <c r="D99">
-        <v>0.1946006829105853</v>
+        <v>0.1946006829105857</v>
       </c>
       <c r="E99">
         <v>19.5</v>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="C100">
-        <v>-0.05614915855311464</v>
+        <v>-0.05614915855311473</v>
       </c>
       <c r="D100">
-        <v>0.02376329598501504</v>
+        <v>0.02376329598501506</v>
       </c>
       <c r="E100">
         <v>2.4</v>
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="C101">
-        <v>-0.3043663239667327</v>
+        <v>-0.3043663239667328</v>
       </c>
       <c r="D101">
         <v>0.1288130976611267</v>
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="C102">
-        <v>-0.4228916956037467</v>
+        <v>-0.4228916956037474</v>
       </c>
       <c r="D102">
-        <v>0.1789750869148024</v>
+        <v>0.1789750869148026</v>
       </c>
       <c r="E102">
         <v>17.9</v>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="C103">
-        <v>0.6024226852787216</v>
+        <v>0.6024226852787207</v>
       </c>
       <c r="D103">
-        <v>0.2549557098851969</v>
+        <v>0.2549557098851964</v>
       </c>
       <c r="E103">
         <v>25.5</v>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="C104">
-        <v>-0.01793718747815283</v>
+        <v>-0.01793718747815288</v>
       </c>
       <c r="D104">
-        <v>0.007591328279280274</v>
+        <v>0.007591328279280293</v>
       </c>
       <c r="E104">
         <v>0.8</v>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="C105">
-        <v>0.05394088085360376</v>
+        <v>0.05394088085360436</v>
       </c>
       <c r="D105">
-        <v>0.02282871463165521</v>
+        <v>0.02282871463165546</v>
       </c>
       <c r="E105">
         <v>2.3</v>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="C106">
-        <v>0.02014396574678898</v>
+        <v>0.0201439657467891</v>
       </c>
       <c r="D106">
-        <v>0.008525275047534933</v>
+        <v>0.008525275047534978</v>
       </c>
       <c r="E106">
         <v>0.9</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="C107">
-        <v>-0.0142256682022456</v>
+        <v>-0.0142256682022461</v>
       </c>
       <c r="D107">
-        <v>0.00602054906583862</v>
+        <v>0.00602054906583883</v>
       </c>
       <c r="E107">
         <v>0.6</v>
@@ -2622,10 +2622,10 @@
         </is>
       </c>
       <c r="C108">
-        <v>-0.01265705804068294</v>
+        <v>-0.01265705804068263</v>
       </c>
       <c r="D108">
-        <v>0.005356686088817246</v>
+        <v>0.005356686088817114</v>
       </c>
       <c r="E108">
         <v>0.5</v>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="C109">
-        <v>-0.01515916976497931</v>
+        <v>-0.01515916976497965</v>
       </c>
       <c r="D109">
-        <v>0.006415623088483697</v>
+        <v>0.006415623088483836</v>
       </c>
       <c r="E109">
         <v>0.6</v>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="C110">
-        <v>-0.02699055824016784</v>
+        <v>-0.02699055824016655</v>
       </c>
       <c r="D110">
-        <v>0.0134676743402714</v>
+        <v>0.0134676743402707</v>
       </c>
       <c r="E110">
         <v>1.3</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="C111">
-        <v>-0.1155308016205869</v>
+        <v>-0.1155308016205919</v>
       </c>
       <c r="D111">
-        <v>0.05764724088518477</v>
+        <v>0.05764724088518698</v>
       </c>
       <c r="E111">
         <v>5.8</v>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="C112">
-        <v>0.01605728442906982</v>
+        <v>0.01605728442907016</v>
       </c>
       <c r="D112">
-        <v>0.008012219516007994</v>
+        <v>0.008012219516008124</v>
       </c>
       <c r="E112">
         <v>0.8</v>
@@ -2727,10 +2727,10 @@
         </is>
       </c>
       <c r="C113">
-        <v>-0.000901961732838929</v>
+        <v>-0.000901961732839171</v>
       </c>
       <c r="D113">
-        <v>0.0004500583788290714</v>
+        <v>0.00045005837882919</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="C114">
-        <v>-0.006520692533923099</v>
+        <v>-0.006520692533923993</v>
       </c>
       <c r="D114">
-        <v>0.003253677183646473</v>
+        <v>0.003253677183646904</v>
       </c>
       <c r="E114">
         <v>0.3</v>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="C115">
-        <v>0.1261216155841644</v>
+        <v>0.126121615584169</v>
       </c>
       <c r="D115">
-        <v>0.06293181603886167</v>
+        <v>0.06293181603886368</v>
       </c>
       <c r="E115">
         <v>6.3</v>
@@ -2793,7 +2793,7 @@
         <v>0.4740676561069609</v>
       </c>
       <c r="D116">
-        <v>0.2365489720847145</v>
+        <v>0.2365489720847134</v>
       </c>
       <c r="E116">
         <v>23.7</v>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="C117">
-        <v>-0.687986208249025</v>
+        <v>-0.6879862082490232</v>
       </c>
       <c r="D117">
-        <v>0.3432894614794152</v>
+        <v>0.3432894614794127</v>
       </c>
       <c r="E117">
         <v>34.3</v>
@@ -2835,7 +2835,7 @@
         <v>0.5208672244657773</v>
       </c>
       <c r="D118">
-        <v>0.2599008916824282</v>
+        <v>0.259900891682427</v>
       </c>
       <c r="E118">
         <v>26</v>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="C119">
-        <v>0.006507172648727898</v>
+        <v>0.006507172648727827</v>
       </c>
       <c r="D119">
-        <v>0.003246931068604812</v>
+        <v>0.003246931068604762</v>
       </c>
       <c r="E119">
         <v>0.3</v>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="C120">
-        <v>0.01636954530689459</v>
+        <v>0.016369545306895</v>
       </c>
       <c r="D120">
-        <v>0.00816803058795139</v>
+        <v>0.008168030587951557</v>
       </c>
       <c r="E120">
         <v>0.8</v>
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="C121">
-        <v>-0.006178692108205557</v>
+        <v>-0.006178692108206287</v>
       </c>
       <c r="D121">
-        <v>0.003083026754084651</v>
+        <v>0.003083026754085001</v>
       </c>
       <c r="E121">
         <v>0.3</v>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="C122">
-        <v>-0.2340435559566853</v>
+        <v>-0.2340435559566849</v>
       </c>
       <c r="D122">
-        <v>0.1109469178407526</v>
+        <v>0.1109469178407518</v>
       </c>
       <c r="E122">
         <v>11.1</v>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="C123">
-        <v>0.7317038429284168</v>
+        <v>0.7317038429284156</v>
       </c>
       <c r="D123">
-        <v>0.3468597364849735</v>
+        <v>0.3468597364849712</v>
       </c>
       <c r="E123">
         <v>34.7</v>
@@ -2961,7 +2961,7 @@
         <v>-0.07686626314254968</v>
       </c>
       <c r="D124">
-        <v>0.03643798243768109</v>
+        <v>0.03643798243768091</v>
       </c>
       <c r="E124">
         <v>3.6</v>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="C125">
-        <v>0.04629018037323861</v>
+        <v>0.04629018037323876</v>
       </c>
       <c r="D125">
-        <v>0.02194357720173164</v>
+        <v>0.0219435772017316</v>
       </c>
       <c r="E125">
         <v>2.2</v>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="C126">
-        <v>0.1086257033686624</v>
+        <v>0.1086257033686627</v>
       </c>
       <c r="D126">
-        <v>0.05149335104644952</v>
+        <v>0.05149335104644941</v>
       </c>
       <c r="E126">
         <v>5.1</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="C127">
-        <v>-0.6018274841889479</v>
+        <v>-0.6018274841889475</v>
       </c>
       <c r="D127">
-        <v>0.2852926420882761</v>
+        <v>0.2852926420882745</v>
       </c>
       <c r="E127">
         <v>28.5</v>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="C128">
-        <v>0.05771973819896489</v>
+        <v>0.05771973819896838</v>
       </c>
       <c r="D128">
-        <v>0.0273616892615299</v>
+        <v>0.02736168926153141</v>
       </c>
       <c r="E128">
         <v>2.7</v>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="C129">
-        <v>-0.139938529431541</v>
+        <v>-0.1399385294315458</v>
       </c>
       <c r="D129">
-        <v>0.06633700493967151</v>
+        <v>0.06633700493967348</v>
       </c>
       <c r="E129">
         <v>6.6</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="C130">
-        <v>0.06253427249908396</v>
+        <v>0.06253427249908763</v>
       </c>
       <c r="D130">
-        <v>0.02964398983269219</v>
+        <v>0.02964398983269378</v>
       </c>
       <c r="E130">
         <v>3</v>
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="C131">
-        <v>0.02194770990563788</v>
+        <v>0.02194770990563806</v>
       </c>
       <c r="D131">
-        <v>0.01040417779391513</v>
+        <v>0.01040417779391516</v>
       </c>
       <c r="E131">
         <v>1</v>
@@ -3126,10 +3126,10 @@
         </is>
       </c>
       <c r="C132">
-        <v>-0.007406828325006286</v>
+        <v>-0.007406828325006512</v>
       </c>
       <c r="D132">
-        <v>0.003511161716356407</v>
+        <v>0.003511161716356496</v>
       </c>
       <c r="E132">
         <v>0.4</v>
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="C133">
-        <v>0.02060520038165768</v>
+        <v>0.02060520038165762</v>
       </c>
       <c r="D133">
-        <v>0.009767769355970251</v>
+        <v>0.009767769355970171</v>
       </c>
       <c r="E133">
         <v>1</v>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="C134">
-        <v>0.01742311914788755</v>
+        <v>0.01742311914788751</v>
       </c>
       <c r="D134">
-        <v>0.00967938520712917</v>
+        <v>0.009679385207129144</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="C135">
-        <v>0.01027234335129659</v>
+        <v>0.01027234335129658</v>
       </c>
       <c r="D135">
-        <v>0.005706783465872539</v>
+        <v>0.005706783465872531</v>
       </c>
       <c r="E135">
         <v>0.6</v>
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="C136">
-        <v>0.01299450557108164</v>
+        <v>0.01299450557108173</v>
       </c>
       <c r="D136">
-        <v>0.007219076213109357</v>
+        <v>0.007219076213109406</v>
       </c>
       <c r="E136">
         <v>0.7</v>
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="C137">
-        <v>-0.02026229614923761</v>
+        <v>-0.02026229614923758</v>
       </c>
       <c r="D137">
-        <v>0.01125668532394672</v>
+        <v>0.0112566853239467</v>
       </c>
       <c r="E137">
         <v>1.1</v>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="C138">
-        <v>-0.01169422501020187</v>
+        <v>-0.01169422501020162</v>
       </c>
       <c r="D138">
-        <v>0.006496707484567244</v>
+        <v>0.006496707484567105</v>
       </c>
       <c r="E138">
         <v>0.6</v>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="C139">
-        <v>-0.01081514862347409</v>
+        <v>-0.01081514862347432</v>
       </c>
       <c r="D139">
-        <v>0.006008338042712108</v>
+        <v>0.006008338042712232</v>
       </c>
       <c r="E139">
         <v>0.6</v>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="C140">
-        <v>-0.0005210294967320212</v>
+        <v>-0.0005210294967322111</v>
       </c>
       <c r="D140">
-        <v>0.0002894570805800491</v>
+        <v>0.0002894570805801544</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="C141">
-        <v>0.0200452001962129</v>
+        <v>0.02004520019621348</v>
       </c>
       <c r="D141">
-        <v>0.01113607802404831</v>
+        <v>0.01113607802404863</v>
       </c>
       <c r="E141">
         <v>1.1</v>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="C142">
-        <v>0.003851626663634298</v>
+        <v>0.003851626663634035</v>
       </c>
       <c r="D142">
-        <v>0.002139764862704635</v>
+        <v>0.002139764862704488</v>
       </c>
       <c r="E142">
         <v>0.2</v>
@@ -3357,10 +3357,10 @@
         </is>
       </c>
       <c r="C143">
-        <v>0.5972195192530133</v>
+        <v>0.5972195192530134</v>
       </c>
       <c r="D143">
-        <v>0.3317843223707329</v>
+        <v>0.3317843223707328</v>
       </c>
       <c r="E143">
         <v>33.2</v>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="C144">
-        <v>0.4021348037119817</v>
+        <v>0.4021348037119818</v>
       </c>
       <c r="D144">
-        <v>0.2234053292801755</v>
+        <v>0.2234053292801754</v>
       </c>
       <c r="E144">
         <v>22.3</v>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="C145">
-        <v>-0.6927895081760009</v>
+        <v>-0.692789508176001</v>
       </c>
       <c r="D145">
-        <v>0.3848780726444215</v>
+        <v>0.3848780726444214</v>
       </c>
       <c r="E145">
         <v>38.5</v>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.412134618020336</v>
+        <v>0.4121346180203361</v>
       </c>
     </row>
     <row r="3">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.2990735352330175</v>
+        <v>0.2990735352330172</v>
       </c>
     </row>
     <row r="4">
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.1065686867467275</v>
+        <v>0.1065686867467277</v>
       </c>
     </row>
     <row r="5">
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.0825452832032275</v>
+        <v>0.08254528320322757</v>
       </c>
     </row>
     <row r="6">
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.0422047727509462</v>
+        <v>0.04220477275094626</v>
       </c>
     </row>
     <row r="7">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.02898434213517002</v>
+        <v>0.02898434213517001</v>
       </c>
     </row>
     <row r="8">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.01506974300524136</v>
+        <v>0.01506974300524133</v>
       </c>
     </row>
     <row r="9">
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.006594951412891327</v>
+        <v>0.006594951412891354</v>
       </c>
     </row>
     <row r="10">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.004450133667540439</v>
+        <v>0.004450133667540445</v>
       </c>
     </row>
     <row r="11">
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.001249432049744514</v>
+        <v>0.001249432049744516</v>
       </c>
     </row>
     <row r="12">
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.001077809388183273</v>
+        <v>0.001077809388183272</v>
       </c>
     </row>
     <row r="13">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>4.669238697427885E-05</v>
+        <v>4.669238697427931E-05</v>
       </c>
     </row>
   </sheetData>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.4232308246826642</v>
+        <v>-0.4232308246826641</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.4006678923088532</v>
+        <v>-0.400667892308853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.1401184370006759</v>
+        <v>-0.140118437000676</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.1289025074023538</v>
+        <v>-0.1289025074023539</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.1119877018990237</v>
+        <v>-0.1119877018990239</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.1061030748001057</v>
+        <v>-0.1061030748001056</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.4957886174245391</v>
+        <v>0.4957886174245394</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.4705749492316099</v>
+        <v>0.4705749492316103</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.4511848358771115</v>
+        <v>0.4511848358771114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.3489079910685441</v>
+        <v>0.3489079910685439</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.1464609058589733</v>
+        <v>-0.1464609058589735</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.1422905354698256</v>
+        <v>-0.1422905354698257</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.1233776143736372</v>
+        <v>-0.1233776143736376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.1069321872223359</v>
+        <v>0.1069321872223361</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
